--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3333333333333333</v>
+        <v>0.475</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4</v>
+        <v>0.460431654676259</v>
       </c>
       <c r="D2">
-        <v>0.75</v>
+        <v>0.6637168141592921</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Llama-3.1-8B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.475</v>
+        <v>0.5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C2">
-        <v>0.460431654676259</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D2">
-        <v>0.6637168141592921</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="E2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
